--- a/po_template/PO VH TEMPLATE.xlsx
+++ b/po_template/PO VH TEMPLATE.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SANGKURIANG\MD_PROJECT\PO\SUPER\po_template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EVERBEST\NEW_GENERATOR\webapp\po_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191BB492-CF6E-4B49-B2D3-D0231DD58444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9000"/>
+    <workbookView xWindow="2115" yWindow="2115" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$H$55</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -26,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -399,14 +398,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="6">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
-    <numFmt numFmtId="166" formatCode="[$￥-804]#,##0"/>
-    <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="168" formatCode="[$￥-804]#,##0"/>
+    <numFmt numFmtId="169" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
   </numFmts>
   <fonts count="34">
     <font>
@@ -1218,275 +1217,260 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="33" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="13" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="29" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="16" fillId="4" borderId="33" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="34" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="18" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
@@ -1495,37 +1479,199 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="13" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1534,184 +1680,22 @@
     <xf numFmtId="4" fontId="13" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="5" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="5" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="5" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="17" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="5" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="5" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="5" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="16" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="16" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="16" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1719,8 +1703,8 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Currency" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="3"/>
-    <cellStyle name="Normal_Book1" xfId="4"/>
+    <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal_Book1" xfId="4" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -1915,7 +1899,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="16"/>
       <tableStyleElement type="headerRow" dxfId="15"/>
       <tableStyleElement type="totalRow" dxfId="14"/>
@@ -1924,7 +1908,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="11"/>
       <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="headerRow" dxfId="9"/>
       <tableStyleElement type="totalRow" dxfId="8"/>
       <tableStyleElement type="firstRowStripe" dxfId="7"/>
@@ -1965,7 +1949,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="42" name="Picture 1"/>
+        <xdr:cNvPr id="42" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2007,7 +1997,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="43" name="AutoShape 54"/>
+        <xdr:cNvPr id="43" name="AutoShape 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00002B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr>
           <a:spLocks noChangeArrowheads="1"/>
         </xdr:cNvSpPr>
@@ -2167,7 +2163,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="62" name="Picture 13"/>
+        <xdr:cNvPr id="62" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2209,7 +2211,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="63" name="Oval 21"/>
+        <xdr:cNvPr id="63" name="Oval 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00003F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2364,7 +2372,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="64" name="Picture 10"/>
+        <xdr:cNvPr id="64" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000040000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2406,7 +2420,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="65" name="Picture 12"/>
+        <xdr:cNvPr id="65" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000041000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2443,7 +2463,13 @@
     <xdr:ext cx="2734310" cy="464820"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="66" name="TextBox 4"/>
+        <xdr:cNvPr id="66" name="TextBox 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000042000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2658,7 +2684,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="71" name="Picture 70"/>
+        <xdr:cNvPr id="71" name="Picture 70">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000047000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2701,7 +2733,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="72" name="Picture 71"/>
+        <xdr:cNvPr id="72" name="Picture 71">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000048000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2744,7 +2782,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="73" name="Picture 72"/>
+        <xdr:cNvPr id="73" name="Picture 72">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000049000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2782,7 +2826,13 @@
     <xdr:ext cx="1664970" cy="299085"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="74" name="TextBox 19"/>
+        <xdr:cNvPr id="74" name="TextBox 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00004A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2946,7 +2996,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Oval 12"/>
+        <xdr:cNvPr id="2" name="Oval 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -3338,690 +3394,672 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P53"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="10" width="40.81640625" customWidth="1"/>
-    <col min="11" max="17" width="20.81640625" customWidth="1"/>
+    <col min="1" max="10" width="40.85546875" customWidth="1"/>
+    <col min="11" max="17" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="25" customHeight="1" thickBot="1">
-      <c r="A1" s="156" t="s">
+    <row r="1" spans="1:16" ht="24.95" customHeight="1" thickBot="1">
+      <c r="A1" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="4" t="s">
+      <c r="B1" s="89"/>
+      <c r="C1" s="90"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="1"/>
-      <c r="P1" s="6"/>
-    </row>
-    <row r="2" spans="1:16" ht="25" customHeight="1">
-      <c r="A2" s="7" t="s">
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="P1" s="5"/>
+    </row>
+    <row r="2" spans="1:16" ht="24.95" customHeight="1">
+      <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="159" t="s">
+      <c r="B2" s="97" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="151"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="8" t="s">
+      <c r="C2" s="98"/>
+      <c r="E2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="1"/>
-      <c r="P2" s="6"/>
-    </row>
-    <row r="3" spans="1:16" ht="25" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" s="160"/>
-      <c r="C3" s="152"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="11"/>
-      <c r="G3" s="12" t="s">
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="P2" s="5"/>
+    </row>
+    <row r="3" spans="1:16" ht="24.95" customHeight="1">
+      <c r="A3" s="9"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="100"/>
+      <c r="E3" s="10"/>
+      <c r="G3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="1"/>
-      <c r="P3" s="6"/>
-    </row>
-    <row r="4" spans="1:16" ht="25" customHeight="1">
-      <c r="A4" s="10" t="s">
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="P3" s="5"/>
+    </row>
+    <row r="4" spans="1:16" ht="24.95" customHeight="1">
+      <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="159" t="s">
+      <c r="B4" s="97" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="151"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="11"/>
-      <c r="G4" s="13" t="s">
+      <c r="C4" s="98"/>
+      <c r="E4" s="10"/>
+      <c r="G4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="1"/>
-      <c r="P4" s="6"/>
-    </row>
-    <row r="5" spans="1:16" ht="25" customHeight="1">
-      <c r="A5" s="10" t="s">
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="P4" s="5"/>
+    </row>
+    <row r="5" spans="1:16" ht="24.95" customHeight="1">
+      <c r="A5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="161" t="s">
+      <c r="B5" s="101" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="153"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="11"/>
-      <c r="G5" s="13" t="s">
+      <c r="C5" s="102"/>
+      <c r="E5" s="10"/>
+      <c r="G5" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="1"/>
-      <c r="P5" s="6"/>
-    </row>
-    <row r="6" spans="1:16" ht="25" customHeight="1" thickBot="1">
-      <c r="A6" s="14"/>
-      <c r="B6" s="154"/>
-      <c r="C6" s="155"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="17"/>
-    </row>
-    <row r="7" spans="1:16" ht="25" customHeight="1" thickBot="1">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="P5" s="5"/>
+    </row>
+    <row r="6" spans="1:16" ht="24.95" customHeight="1" thickBot="1">
+      <c r="A6" s="13"/>
+      <c r="B6" s="103"/>
+      <c r="C6" s="104"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="16"/>
+    </row>
+    <row r="7" spans="1:16" ht="24.95" customHeight="1" thickBot="1">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:16" ht="30" customHeight="1">
-      <c r="A8" s="109" t="s">
+      <c r="A8" s="108" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="114" t="s">
+      <c r="B8" s="113" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="114" t="s">
+      <c r="C8" s="113" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="93" t="s">
+      <c r="D8" s="142" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="96" t="s">
+      <c r="E8" s="145" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="98" t="s">
+      <c r="F8" s="147" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="100" t="s">
+      <c r="G8" s="149" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="30" customHeight="1">
-      <c r="A9" s="110"/>
-      <c r="B9" s="115"/>
-      <c r="C9" s="115"/>
-      <c r="D9" s="94"/>
-      <c r="E9" s="97"/>
-      <c r="F9" s="99"/>
-      <c r="G9" s="101"/>
+      <c r="A9" s="109"/>
+      <c r="B9" s="114"/>
+      <c r="C9" s="114"/>
+      <c r="D9" s="143"/>
+      <c r="E9" s="146"/>
+      <c r="F9" s="148"/>
+      <c r="G9" s="150"/>
     </row>
     <row r="10" spans="1:16" ht="30" customHeight="1">
-      <c r="A10" s="111"/>
-      <c r="B10" s="18" t="s">
+      <c r="A10" s="110"/>
+      <c r="B10" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="95"/>
-      <c r="E10" s="19" t="s">
+      <c r="D10" s="144"/>
+      <c r="E10" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="F10" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="20" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="30" customHeight="1">
-      <c r="A11" s="112"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="25">
+      <c r="A11" s="111"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="24">
         <v>0</v>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="25">
         <f t="shared" ref="G11:G14" si="0">F11*E11</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="30" customHeight="1">
-      <c r="A12" s="113"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="25">
+      <c r="A12" s="112"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="24">
         <v>0</v>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="30" customHeight="1">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="25">
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="24">
         <v>0</v>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="30" customHeight="1">
-      <c r="A14" s="33" t="s">
+      <c r="A14" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="25">
+      <c r="B14" s="33"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="24">
         <v>0</v>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="30" customHeight="1">
-      <c r="A15" s="36"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="37">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="35">
         <f>SUM(E11:E14)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="38"/>
-      <c r="G15" s="39">
+      <c r="F15" s="36"/>
+      <c r="G15" s="37">
         <f>SUM(G11:G14)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="40"/>
-    </row>
-    <row r="16" spans="1:16" ht="25" customHeight="1">
-      <c r="A16" s="36"/>
-      <c r="B16" s="36"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="36"/>
+      <c r="H15" s="11"/>
+    </row>
+    <row r="16" spans="1:16" ht="24.95" customHeight="1">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" ht="30" customHeight="1">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="102"/>
-      <c r="C17" s="103"/>
-      <c r="D17" s="42" t="s">
+      <c r="B17" s="151"/>
+      <c r="C17" s="152"/>
+      <c r="D17" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="43" t="s">
+      <c r="E17" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="129" t="s">
+      <c r="F17" s="155" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="130"/>
+      <c r="G17" s="156"/>
     </row>
     <row r="18" spans="1:8" ht="30" customHeight="1">
-      <c r="A18" s="44" t="s">
+      <c r="A18" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="104"/>
-      <c r="C18" s="105"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="47"/>
+      <c r="B18" s="153"/>
+      <c r="C18" s="154"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="44"/>
     </row>
     <row r="19" spans="1:8" ht="30" customHeight="1">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="49"/>
-      <c r="C19" s="50"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="51"/>
+      <c r="B19" s="46"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="48"/>
     </row>
     <row r="20" spans="1:8" ht="30" customHeight="1">
-      <c r="A20" s="52" t="s">
+      <c r="A20" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="53"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="45"/>
-      <c r="F20" s="45"/>
-      <c r="G20" s="51"/>
+      <c r="B20" s="50"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="48"/>
     </row>
     <row r="21" spans="1:8" ht="30" customHeight="1">
-      <c r="A21" s="55" t="s">
+      <c r="A21" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="116" t="s">
+      <c r="B21" s="115" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="117"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="51"/>
+      <c r="C21" s="116"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="48"/>
     </row>
     <row r="22" spans="1:8" ht="30" customHeight="1">
-      <c r="A22" s="56"/>
-      <c r="B22" s="118"/>
-      <c r="C22" s="119"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="51"/>
+      <c r="A22" s="53"/>
+      <c r="B22" s="117"/>
+      <c r="C22" s="118"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="48"/>
     </row>
     <row r="23" spans="1:8" ht="30" customHeight="1">
-      <c r="A23" s="57" t="s">
+      <c r="A23" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="50"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="51"/>
+      <c r="B23" s="46"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="48"/>
     </row>
     <row r="24" spans="1:8" ht="30" customHeight="1">
-      <c r="A24" s="57" t="s">
+      <c r="A24" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="B24" s="58"/>
-      <c r="C24" s="59"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="51"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="55"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="48"/>
     </row>
     <row r="25" spans="1:8" ht="30" customHeight="1">
-      <c r="A25" s="60"/>
-      <c r="B25" s="61"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="63"/>
-      <c r="E25" s="63"/>
-      <c r="F25" s="63"/>
-      <c r="G25" s="64"/>
-    </row>
-    <row r="26" spans="1:8" ht="25" customHeight="1">
-      <c r="A26" s="65"/>
-      <c r="B26" s="65"/>
-      <c r="C26" s="66"/>
-      <c r="D26" s="66"/>
-      <c r="E26" s="67"/>
-      <c r="F26" s="36"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="36"/>
-    </row>
-    <row r="27" spans="1:8" ht="25" customHeight="1">
-      <c r="A27" s="131" t="s">
+      <c r="A25" s="56"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="58"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="60"/>
+    </row>
+    <row r="26" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A26" s="61"/>
+      <c r="B26" s="61"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="63"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A27" s="128" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="132"/>
-      <c r="C27" s="132"/>
-      <c r="D27" s="132"/>
-      <c r="E27" s="132"/>
-      <c r="F27" s="132"/>
-      <c r="G27" s="132"/>
-      <c r="H27" s="133"/>
-    </row>
-    <row r="28" spans="1:8" ht="25" customHeight="1">
-      <c r="A28" s="134">
+      <c r="B27" s="129"/>
+      <c r="C27" s="129"/>
+      <c r="D27" s="129"/>
+      <c r="E27" s="129"/>
+      <c r="F27" s="129"/>
+      <c r="G27" s="129"/>
+      <c r="H27" s="130"/>
+    </row>
+    <row r="28" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A28" s="131">
         <f>B11</f>
         <v>0</v>
       </c>
-      <c r="B28" s="135"/>
-      <c r="C28" s="135"/>
-      <c r="D28" s="135"/>
-      <c r="E28" s="135"/>
-      <c r="F28" s="135"/>
-      <c r="G28" s="135"/>
-      <c r="H28" s="136"/>
-    </row>
-    <row r="29" spans="1:8" ht="25" customHeight="1">
-      <c r="A29" s="134">
+      <c r="B28" s="132"/>
+      <c r="C28" s="132"/>
+      <c r="D28" s="132"/>
+      <c r="E28" s="132"/>
+      <c r="F28" s="132"/>
+      <c r="G28" s="132"/>
+      <c r="H28" s="133"/>
+    </row>
+    <row r="29" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A29" s="131">
         <f>C11</f>
         <v>0</v>
       </c>
-      <c r="B29" s="135"/>
-      <c r="C29" s="135"/>
-      <c r="D29" s="135"/>
-      <c r="E29" s="135"/>
-      <c r="F29" s="135"/>
-      <c r="G29" s="135"/>
-      <c r="H29" s="136"/>
-    </row>
-    <row r="30" spans="1:8" ht="25" customHeight="1">
-      <c r="A30" s="120"/>
-      <c r="B30" s="121"/>
-      <c r="C30" s="120"/>
-      <c r="D30" s="126"/>
-      <c r="E30" s="142"/>
-      <c r="F30" s="143"/>
-      <c r="G30" s="142"/>
-      <c r="H30" s="148"/>
-    </row>
-    <row r="31" spans="1:8" ht="25" customHeight="1">
-      <c r="A31" s="122"/>
-      <c r="B31" s="123"/>
-      <c r="C31" s="122"/>
-      <c r="D31" s="127"/>
-      <c r="E31" s="144"/>
-      <c r="F31" s="145"/>
-      <c r="G31" s="144"/>
-      <c r="H31" s="149"/>
-    </row>
-    <row r="32" spans="1:8" ht="25" customHeight="1">
-      <c r="A32" s="122"/>
-      <c r="B32" s="123"/>
-      <c r="C32" s="122"/>
-      <c r="D32" s="127"/>
-      <c r="E32" s="144"/>
-      <c r="F32" s="145"/>
-      <c r="G32" s="144"/>
-      <c r="H32" s="149"/>
-    </row>
-    <row r="33" spans="1:8" ht="25" customHeight="1">
-      <c r="A33" s="122"/>
-      <c r="B33" s="123"/>
-      <c r="C33" s="122"/>
-      <c r="D33" s="127"/>
-      <c r="E33" s="144"/>
-      <c r="F33" s="145"/>
-      <c r="G33" s="144"/>
-      <c r="H33" s="149"/>
-    </row>
-    <row r="34" spans="1:8" ht="25" customHeight="1">
-      <c r="A34" s="122"/>
-      <c r="B34" s="123"/>
-      <c r="C34" s="122"/>
-      <c r="D34" s="127"/>
-      <c r="E34" s="144"/>
-      <c r="F34" s="145"/>
-      <c r="G34" s="144"/>
-      <c r="H34" s="149"/>
-    </row>
-    <row r="35" spans="1:8" ht="25" customHeight="1">
-      <c r="A35" s="122"/>
-      <c r="B35" s="123"/>
-      <c r="C35" s="122"/>
-      <c r="D35" s="127"/>
-      <c r="E35" s="144"/>
-      <c r="F35" s="145"/>
-      <c r="G35" s="144"/>
-      <c r="H35" s="149"/>
-    </row>
-    <row r="36" spans="1:8" ht="25" customHeight="1">
-      <c r="A36" s="122"/>
-      <c r="B36" s="123"/>
-      <c r="C36" s="122"/>
-      <c r="D36" s="127"/>
-      <c r="E36" s="144"/>
-      <c r="F36" s="145"/>
-      <c r="G36" s="144"/>
-      <c r="H36" s="149"/>
-    </row>
-    <row r="37" spans="1:8" ht="25" customHeight="1">
-      <c r="A37" s="124"/>
-      <c r="B37" s="125"/>
-      <c r="C37" s="124"/>
-      <c r="D37" s="128"/>
-      <c r="E37" s="146"/>
-      <c r="F37" s="147"/>
-      <c r="G37" s="146"/>
-      <c r="H37" s="150"/>
-    </row>
-    <row r="38" spans="1:8" ht="25" customHeight="1">
-      <c r="A38" s="137">
+      <c r="B29" s="132"/>
+      <c r="C29" s="132"/>
+      <c r="D29" s="132"/>
+      <c r="E29" s="132"/>
+      <c r="F29" s="132"/>
+      <c r="G29" s="132"/>
+      <c r="H29" s="133"/>
+    </row>
+    <row r="30" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A30" s="119"/>
+      <c r="B30" s="120"/>
+      <c r="C30" s="119"/>
+      <c r="D30" s="125"/>
+      <c r="E30" s="91"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="91"/>
+      <c r="H30" s="92"/>
+    </row>
+    <row r="31" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A31" s="121"/>
+      <c r="B31" s="122"/>
+      <c r="C31" s="121"/>
+      <c r="D31" s="126"/>
+      <c r="E31" s="93"/>
+      <c r="F31" s="140"/>
+      <c r="G31" s="93"/>
+      <c r="H31" s="94"/>
+    </row>
+    <row r="32" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A32" s="121"/>
+      <c r="B32" s="122"/>
+      <c r="C32" s="121"/>
+      <c r="D32" s="126"/>
+      <c r="E32" s="93"/>
+      <c r="F32" s="140"/>
+      <c r="G32" s="93"/>
+      <c r="H32" s="94"/>
+    </row>
+    <row r="33" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A33" s="121"/>
+      <c r="B33" s="122"/>
+      <c r="C33" s="121"/>
+      <c r="D33" s="126"/>
+      <c r="E33" s="93"/>
+      <c r="F33" s="140"/>
+      <c r="G33" s="93"/>
+      <c r="H33" s="94"/>
+    </row>
+    <row r="34" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A34" s="121"/>
+      <c r="B34" s="122"/>
+      <c r="C34" s="121"/>
+      <c r="D34" s="126"/>
+      <c r="E34" s="93"/>
+      <c r="F34" s="140"/>
+      <c r="G34" s="93"/>
+      <c r="H34" s="94"/>
+    </row>
+    <row r="35" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A35" s="121"/>
+      <c r="B35" s="122"/>
+      <c r="C35" s="121"/>
+      <c r="D35" s="126"/>
+      <c r="E35" s="93"/>
+      <c r="F35" s="140"/>
+      <c r="G35" s="93"/>
+      <c r="H35" s="94"/>
+    </row>
+    <row r="36" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A36" s="121"/>
+      <c r="B36" s="122"/>
+      <c r="C36" s="121"/>
+      <c r="D36" s="126"/>
+      <c r="E36" s="93"/>
+      <c r="F36" s="140"/>
+      <c r="G36" s="93"/>
+      <c r="H36" s="94"/>
+    </row>
+    <row r="37" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A37" s="123"/>
+      <c r="B37" s="124"/>
+      <c r="C37" s="123"/>
+      <c r="D37" s="127"/>
+      <c r="E37" s="95"/>
+      <c r="F37" s="141"/>
+      <c r="G37" s="95"/>
+      <c r="H37" s="96"/>
+    </row>
+    <row r="38" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A38" s="134">
         <f>D11</f>
         <v>0</v>
       </c>
-      <c r="B38" s="138"/>
-      <c r="C38" s="139">
+      <c r="B38" s="135"/>
+      <c r="C38" s="136">
         <f>D12</f>
         <v>0</v>
       </c>
-      <c r="D38" s="140"/>
-      <c r="E38" s="139">
+      <c r="D38" s="137"/>
+      <c r="E38" s="136">
         <f>D13</f>
         <v>0</v>
       </c>
-      <c r="F38" s="141"/>
-      <c r="G38" s="139">
+      <c r="F38" s="138"/>
+      <c r="G38" s="136">
         <f>D14</f>
         <v>0</v>
       </c>
-      <c r="H38" s="141"/>
-    </row>
-    <row r="39" spans="1:8" ht="25" customHeight="1">
-      <c r="A39" s="68" t="s">
+      <c r="H38" s="138"/>
+    </row>
+    <row r="39" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A39" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="69"/>
-      <c r="C39" s="69"/>
-      <c r="D39" s="69"/>
-      <c r="E39" s="69"/>
-      <c r="F39" s="69"/>
-      <c r="G39" s="68" t="s">
+      <c r="B39" s="65"/>
+      <c r="C39" s="65"/>
+      <c r="D39" s="65"/>
+      <c r="E39" s="65"/>
+      <c r="F39" s="65"/>
+      <c r="G39" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="H39" s="70"/>
-    </row>
-    <row r="40" spans="1:8" ht="25" customHeight="1">
-      <c r="A40" s="71"/>
-      <c r="B40" s="72"/>
-      <c r="C40" s="72"/>
-      <c r="D40" s="72"/>
-      <c r="E40" s="72"/>
-      <c r="F40" s="72"/>
-      <c r="G40" s="73" t="s">
+      <c r="H39" s="66"/>
+    </row>
+    <row r="40" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A40" s="67"/>
+      <c r="B40" s="68"/>
+      <c r="C40" s="68"/>
+      <c r="D40" s="68"/>
+      <c r="E40" s="68"/>
+      <c r="F40" s="68"/>
+      <c r="G40" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="H40" s="74"/>
-    </row>
-    <row r="41" spans="1:8" ht="25" customHeight="1">
-      <c r="A41" s="75"/>
-      <c r="B41" s="76"/>
-      <c r="C41" s="77"/>
-      <c r="D41" s="76"/>
-      <c r="E41" s="78"/>
-      <c r="F41" s="76"/>
-      <c r="G41" s="79" t="s">
+      <c r="H40" s="70"/>
+    </row>
+    <row r="41" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A41" s="71"/>
+      <c r="B41" s="72"/>
+      <c r="C41" s="73"/>
+      <c r="D41" s="72"/>
+      <c r="E41" s="74"/>
+      <c r="F41" s="72"/>
+      <c r="G41" s="75" t="s">
         <v>40</v>
       </c>
-      <c r="H41" s="77"/>
-    </row>
-    <row r="42" spans="1:8" ht="25" customHeight="1">
-      <c r="A42" s="80"/>
-      <c r="B42" s="36"/>
-      <c r="C42" s="81"/>
-      <c r="D42" s="36"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="82" t="s">
+      <c r="H41" s="73"/>
+    </row>
+    <row r="42" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A42" s="76"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="77"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="H42" s="81"/>
-    </row>
-    <row r="43" spans="1:8" ht="25" customHeight="1">
-      <c r="A43" s="80"/>
-      <c r="B43" s="36"/>
-      <c r="C43" s="81"/>
-      <c r="D43" s="36"/>
-      <c r="E43" s="36"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="83"/>
-      <c r="H43" s="81"/>
-    </row>
-    <row r="44" spans="1:8" ht="25" customHeight="1">
-      <c r="A44" s="80"/>
-      <c r="B44" s="36"/>
-      <c r="C44" s="81"/>
-      <c r="D44" s="36"/>
-      <c r="E44" s="36"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="83" t="s">
+      <c r="H42" s="77"/>
+    </row>
+    <row r="43" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A43" s="76"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="77"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="79"/>
+      <c r="H43" s="77"/>
+    </row>
+    <row r="44" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A44" s="76"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="77"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="79" t="s">
         <v>42</v>
       </c>
-      <c r="H44" s="81"/>
-    </row>
-    <row r="45" spans="1:8" ht="25" customHeight="1">
-      <c r="A45" s="80"/>
-      <c r="B45" s="36"/>
-      <c r="C45" s="81"/>
-      <c r="D45" s="36"/>
-      <c r="E45" s="84"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="82" t="s">
+      <c r="H44" s="77"/>
+    </row>
+    <row r="45" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A45" s="76"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="77"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="H45" s="81"/>
-    </row>
-    <row r="46" spans="1:8" ht="25" customHeight="1">
-      <c r="A46" s="80"/>
-      <c r="B46" s="36"/>
-      <c r="C46" s="81"/>
-      <c r="D46" s="36"/>
-      <c r="E46" s="67"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="83"/>
-      <c r="H46" s="81"/>
-    </row>
-    <row r="47" spans="1:8" ht="25" customHeight="1">
-      <c r="A47" s="80"/>
-      <c r="B47" s="36"/>
-      <c r="C47" s="81"/>
-      <c r="D47" s="36"/>
-      <c r="E47" s="67"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="83" t="s">
+      <c r="H45" s="77"/>
+    </row>
+    <row r="46" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A46" s="76"/>
+      <c r="B46" s="4"/>
+      <c r="C46" s="77"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="63"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="79"/>
+      <c r="H46" s="77"/>
+    </row>
+    <row r="47" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A47" s="76"/>
+      <c r="B47" s="4"/>
+      <c r="C47" s="77"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="63"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="H47" s="81"/>
-    </row>
-    <row r="48" spans="1:8" ht="25" customHeight="1">
-      <c r="A48" s="80"/>
-      <c r="B48" s="36"/>
-      <c r="C48" s="81"/>
-      <c r="D48" s="36"/>
-      <c r="E48" s="67"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="85"/>
-      <c r="H48" s="81"/>
-    </row>
-    <row r="49" spans="1:8" ht="25" customHeight="1">
-      <c r="A49" s="80"/>
-      <c r="B49" s="36"/>
-      <c r="C49" s="81"/>
-      <c r="D49" s="36"/>
-      <c r="E49" s="67"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="80"/>
-      <c r="H49" s="81"/>
-    </row>
-    <row r="50" spans="1:8" ht="25" customHeight="1">
-      <c r="A50" s="80"/>
-      <c r="B50" s="36"/>
-      <c r="C50" s="81"/>
-      <c r="D50" s="36"/>
-      <c r="E50" s="67"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="80"/>
-      <c r="H50" s="81"/>
-    </row>
-    <row r="51" spans="1:8" ht="25" customHeight="1">
-      <c r="A51" s="80"/>
-      <c r="B51" s="36"/>
-      <c r="C51" s="86"/>
-      <c r="D51" s="36"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="80"/>
-      <c r="H51" s="81"/>
-    </row>
-    <row r="52" spans="1:8" ht="25" customHeight="1">
-      <c r="A52" s="87"/>
-      <c r="C52" s="88"/>
-      <c r="D52" s="36"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="80"/>
-      <c r="H52" s="81"/>
-    </row>
-    <row r="53" spans="1:8" ht="25" customHeight="1">
-      <c r="A53" s="106" t="s">
+      <c r="H47" s="77"/>
+    </row>
+    <row r="48" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A48" s="76"/>
+      <c r="B48" s="4"/>
+      <c r="C48" s="77"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="63"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="80"/>
+      <c r="H48" s="77"/>
+    </row>
+    <row r="49" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A49" s="76"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="77"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="63"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="76"/>
+      <c r="H49" s="77"/>
+    </row>
+    <row r="50" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A50" s="76"/>
+      <c r="B50" s="4"/>
+      <c r="C50" s="77"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="63"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="77"/>
+    </row>
+    <row r="51" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A51" s="76"/>
+      <c r="B51" s="4"/>
+      <c r="C51" s="81"/>
+      <c r="D51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="76"/>
+      <c r="H51" s="77"/>
+    </row>
+    <row r="52" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A52" s="82"/>
+      <c r="C52" s="83"/>
+      <c r="D52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="76"/>
+      <c r="H52" s="77"/>
+    </row>
+    <row r="53" spans="1:8" ht="24.95" customHeight="1">
+      <c r="A53" s="105" t="s">
         <v>45</v>
       </c>
-      <c r="B53" s="107"/>
-      <c r="C53" s="108"/>
-      <c r="D53" s="89"/>
-      <c r="E53" s="90"/>
-      <c r="F53" s="89"/>
-      <c r="G53" s="91"/>
-      <c r="H53" s="92"/>
+      <c r="B53" s="106"/>
+      <c r="C53" s="107"/>
+      <c r="D53" s="84"/>
+      <c r="E53" s="85"/>
+      <c r="F53" s="84"/>
+      <c r="G53" s="86"/>
+      <c r="H53" s="87"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="G30:H37"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
     <mergeCell ref="A53:C53"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A11:A12"/>
@@ -4038,6 +4076,13 @@
     <mergeCell ref="E38:F38"/>
     <mergeCell ref="G38:H38"/>
     <mergeCell ref="E30:F37"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="G30:H37"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="D8:D10"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="F8:F9"/>
@@ -4046,8 +4091,8 @@
     <mergeCell ref="F17:G17"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.3" footer="0.3"/>
-  <pageSetup scale="36" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.11811023622047245" bottom="0.11811023622047245" header="0.11811023622047245" footer="0.11811023622047245"/>
+  <pageSetup paperSize="9" scale="36" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/po_template/PO VH TEMPLATE.xlsx
+++ b/po_template/PO VH TEMPLATE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EVERBEST\NEW_GENERATOR\webapp\po_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191BB492-CF6E-4B49-B2D3-D0231DD58444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF8EA150-129F-4FFD-ADF4-AD6F4F376941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2115" yWindow="2115" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1491,6 +1491,126 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1500,19 +1620,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1541,117 +1652,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3403,11 +3403,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="24.95" customHeight="1" thickBot="1">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="128" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="89"/>
-      <c r="C1" s="90"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="130"/>
       <c r="E1" s="1"/>
       <c r="F1" s="2"/>
       <c r="G1" s="3" t="s">
@@ -3421,10 +3421,10 @@
       <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="97" t="s">
+      <c r="B2" s="134" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="98"/>
+      <c r="C2" s="135"/>
       <c r="E2" s="7" t="s">
         <v>4</v>
       </c>
@@ -3437,8 +3437,8 @@
     </row>
     <row r="3" spans="1:16" ht="24.95" customHeight="1">
       <c r="A3" s="9"/>
-      <c r="B3" s="99"/>
-      <c r="C3" s="100"/>
+      <c r="B3" s="136"/>
+      <c r="C3" s="137"/>
       <c r="E3" s="10"/>
       <c r="G3" s="11" t="s">
         <v>6</v>
@@ -3451,10 +3451,10 @@
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="97" t="s">
+      <c r="B4" s="134" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="98"/>
+      <c r="C4" s="135"/>
       <c r="E4" s="10"/>
       <c r="G4" s="12" t="s">
         <v>8</v>
@@ -3467,10 +3467,10 @@
       <c r="A5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="101" t="s">
+      <c r="B5" s="138" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="102"/>
+      <c r="C5" s="139"/>
       <c r="E5" s="10"/>
       <c r="G5" s="12" t="s">
         <v>11</v>
@@ -3481,8 +3481,8 @@
     </row>
     <row r="6" spans="1:16" ht="24.95" customHeight="1" thickBot="1">
       <c r="A6" s="13"/>
-      <c r="B6" s="103"/>
-      <c r="C6" s="104"/>
+      <c r="B6" s="140"/>
+      <c r="C6" s="141"/>
       <c r="E6" s="14"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
@@ -3504,13 +3504,13 @@
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:16" ht="30" customHeight="1">
-      <c r="A8" s="108" t="s">
+      <c r="A8" s="91" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="113" t="s">
+      <c r="B8" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="113" t="s">
+      <c r="C8" s="96" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="142" t="s">
@@ -3527,16 +3527,16 @@
       </c>
     </row>
     <row r="9" spans="1:16" ht="30" customHeight="1">
-      <c r="A9" s="109"/>
-      <c r="B9" s="114"/>
-      <c r="C9" s="114"/>
+      <c r="A9" s="92"/>
+      <c r="B9" s="97"/>
+      <c r="C9" s="97"/>
       <c r="D9" s="143"/>
       <c r="E9" s="146"/>
       <c r="F9" s="148"/>
       <c r="G9" s="150"/>
     </row>
     <row r="10" spans="1:16" ht="30" customHeight="1">
-      <c r="A10" s="110"/>
+      <c r="A10" s="93"/>
       <c r="B10" s="17" t="s">
         <v>19</v>
       </c>
@@ -3555,7 +3555,7 @@
       </c>
     </row>
     <row r="11" spans="1:16" ht="30" customHeight="1">
-      <c r="A11" s="111"/>
+      <c r="A11" s="94"/>
       <c r="B11" s="21"/>
       <c r="C11" s="21"/>
       <c r="D11" s="22"/>
@@ -3569,7 +3569,7 @@
       </c>
     </row>
     <row r="12" spans="1:16" ht="30" customHeight="1">
-      <c r="A12" s="112"/>
+      <c r="A12" s="95"/>
       <c r="B12" s="26"/>
       <c r="C12" s="27"/>
       <c r="D12" s="28"/>
@@ -3694,10 +3694,10 @@
       <c r="A21" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="115" t="s">
+      <c r="B21" s="98" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="116"/>
+      <c r="C21" s="99"/>
       <c r="D21" s="42"/>
       <c r="E21" s="42"/>
       <c r="F21" s="42"/>
@@ -3705,8 +3705,8 @@
     </row>
     <row r="22" spans="1:8" ht="30" customHeight="1">
       <c r="A22" s="53"/>
-      <c r="B22" s="117"/>
-      <c r="C22" s="118"/>
+      <c r="B22" s="100"/>
+      <c r="C22" s="101"/>
       <c r="D22" s="42"/>
       <c r="E22" s="42"/>
       <c r="F22" s="42"/>
@@ -3754,144 +3754,144 @@
       <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A27" s="128" t="s">
+      <c r="A27" s="111" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="129"/>
-      <c r="C27" s="129"/>
-      <c r="D27" s="129"/>
-      <c r="E27" s="129"/>
-      <c r="F27" s="129"/>
-      <c r="G27" s="129"/>
-      <c r="H27" s="130"/>
+      <c r="B27" s="112"/>
+      <c r="C27" s="112"/>
+      <c r="D27" s="112"/>
+      <c r="E27" s="112"/>
+      <c r="F27" s="112"/>
+      <c r="G27" s="112"/>
+      <c r="H27" s="113"/>
     </row>
     <row r="28" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A28" s="131">
+      <c r="A28" s="114">
         <f>B11</f>
         <v>0</v>
       </c>
-      <c r="B28" s="132"/>
-      <c r="C28" s="132"/>
-      <c r="D28" s="132"/>
-      <c r="E28" s="132"/>
-      <c r="F28" s="132"/>
-      <c r="G28" s="132"/>
-      <c r="H28" s="133"/>
+      <c r="B28" s="115"/>
+      <c r="C28" s="115"/>
+      <c r="D28" s="115"/>
+      <c r="E28" s="115"/>
+      <c r="F28" s="115"/>
+      <c r="G28" s="115"/>
+      <c r="H28" s="116"/>
     </row>
     <row r="29" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A29" s="131">
+      <c r="A29" s="114">
         <f>C11</f>
         <v>0</v>
       </c>
-      <c r="B29" s="132"/>
-      <c r="C29" s="132"/>
-      <c r="D29" s="132"/>
-      <c r="E29" s="132"/>
-      <c r="F29" s="132"/>
-      <c r="G29" s="132"/>
-      <c r="H29" s="133"/>
+      <c r="B29" s="115"/>
+      <c r="C29" s="115"/>
+      <c r="D29" s="115"/>
+      <c r="E29" s="115"/>
+      <c r="F29" s="115"/>
+      <c r="G29" s="115"/>
+      <c r="H29" s="116"/>
     </row>
     <row r="30" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A30" s="119"/>
-      <c r="B30" s="120"/>
-      <c r="C30" s="119"/>
-      <c r="D30" s="125"/>
-      <c r="E30" s="91"/>
-      <c r="F30" s="139"/>
-      <c r="G30" s="91"/>
-      <c r="H30" s="92"/>
+      <c r="A30" s="102"/>
+      <c r="B30" s="103"/>
+      <c r="C30" s="102"/>
+      <c r="D30" s="108"/>
+      <c r="E30" s="122"/>
+      <c r="F30" s="123"/>
+      <c r="G30" s="122"/>
+      <c r="H30" s="131"/>
     </row>
     <row r="31" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A31" s="121"/>
-      <c r="B31" s="122"/>
-      <c r="C31" s="121"/>
-      <c r="D31" s="126"/>
-      <c r="E31" s="93"/>
-      <c r="F31" s="140"/>
-      <c r="G31" s="93"/>
-      <c r="H31" s="94"/>
+      <c r="A31" s="104"/>
+      <c r="B31" s="105"/>
+      <c r="C31" s="104"/>
+      <c r="D31" s="109"/>
+      <c r="E31" s="124"/>
+      <c r="F31" s="125"/>
+      <c r="G31" s="124"/>
+      <c r="H31" s="132"/>
     </row>
     <row r="32" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A32" s="121"/>
-      <c r="B32" s="122"/>
-      <c r="C32" s="121"/>
-      <c r="D32" s="126"/>
-      <c r="E32" s="93"/>
-      <c r="F32" s="140"/>
-      <c r="G32" s="93"/>
-      <c r="H32" s="94"/>
+      <c r="A32" s="104"/>
+      <c r="B32" s="105"/>
+      <c r="C32" s="104"/>
+      <c r="D32" s="109"/>
+      <c r="E32" s="124"/>
+      <c r="F32" s="125"/>
+      <c r="G32" s="124"/>
+      <c r="H32" s="132"/>
     </row>
     <row r="33" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A33" s="121"/>
-      <c r="B33" s="122"/>
-      <c r="C33" s="121"/>
-      <c r="D33" s="126"/>
-      <c r="E33" s="93"/>
-      <c r="F33" s="140"/>
-      <c r="G33" s="93"/>
-      <c r="H33" s="94"/>
+      <c r="A33" s="104"/>
+      <c r="B33" s="105"/>
+      <c r="C33" s="104"/>
+      <c r="D33" s="109"/>
+      <c r="E33" s="124"/>
+      <c r="F33" s="125"/>
+      <c r="G33" s="124"/>
+      <c r="H33" s="132"/>
     </row>
     <row r="34" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A34" s="121"/>
-      <c r="B34" s="122"/>
-      <c r="C34" s="121"/>
-      <c r="D34" s="126"/>
-      <c r="E34" s="93"/>
-      <c r="F34" s="140"/>
-      <c r="G34" s="93"/>
-      <c r="H34" s="94"/>
+      <c r="A34" s="104"/>
+      <c r="B34" s="105"/>
+      <c r="C34" s="104"/>
+      <c r="D34" s="109"/>
+      <c r="E34" s="124"/>
+      <c r="F34" s="125"/>
+      <c r="G34" s="124"/>
+      <c r="H34" s="132"/>
     </row>
     <row r="35" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A35" s="121"/>
-      <c r="B35" s="122"/>
-      <c r="C35" s="121"/>
-      <c r="D35" s="126"/>
-      <c r="E35" s="93"/>
-      <c r="F35" s="140"/>
-      <c r="G35" s="93"/>
-      <c r="H35" s="94"/>
+      <c r="A35" s="104"/>
+      <c r="B35" s="105"/>
+      <c r="C35" s="104"/>
+      <c r="D35" s="109"/>
+      <c r="E35" s="124"/>
+      <c r="F35" s="125"/>
+      <c r="G35" s="124"/>
+      <c r="H35" s="132"/>
     </row>
     <row r="36" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A36" s="121"/>
-      <c r="B36" s="122"/>
-      <c r="C36" s="121"/>
-      <c r="D36" s="126"/>
-      <c r="E36" s="93"/>
-      <c r="F36" s="140"/>
-      <c r="G36" s="93"/>
-      <c r="H36" s="94"/>
+      <c r="A36" s="104"/>
+      <c r="B36" s="105"/>
+      <c r="C36" s="104"/>
+      <c r="D36" s="109"/>
+      <c r="E36" s="124"/>
+      <c r="F36" s="125"/>
+      <c r="G36" s="124"/>
+      <c r="H36" s="132"/>
     </row>
     <row r="37" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A37" s="123"/>
-      <c r="B37" s="124"/>
-      <c r="C37" s="123"/>
-      <c r="D37" s="127"/>
-      <c r="E37" s="95"/>
-      <c r="F37" s="141"/>
-      <c r="G37" s="95"/>
-      <c r="H37" s="96"/>
+      <c r="A37" s="106"/>
+      <c r="B37" s="107"/>
+      <c r="C37" s="106"/>
+      <c r="D37" s="110"/>
+      <c r="E37" s="126"/>
+      <c r="F37" s="127"/>
+      <c r="G37" s="126"/>
+      <c r="H37" s="133"/>
     </row>
     <row r="38" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A38" s="134">
+      <c r="A38" s="117">
         <f>D11</f>
         <v>0</v>
       </c>
-      <c r="B38" s="135"/>
-      <c r="C38" s="136">
+      <c r="B38" s="118"/>
+      <c r="C38" s="119">
         <f>D12</f>
         <v>0</v>
       </c>
-      <c r="D38" s="137"/>
-      <c r="E38" s="136">
+      <c r="D38" s="120"/>
+      <c r="E38" s="119">
         <f>D13</f>
         <v>0</v>
       </c>
-      <c r="F38" s="138"/>
-      <c r="G38" s="136">
+      <c r="F38" s="121"/>
+      <c r="G38" s="119">
         <f>D14</f>
         <v>0</v>
       </c>
-      <c r="H38" s="138"/>
+      <c r="H38" s="121"/>
     </row>
     <row r="39" spans="1:8" ht="24.95" customHeight="1">
       <c r="A39" s="64" t="s">
@@ -4047,11 +4047,11 @@
       <c r="H52" s="77"/>
     </row>
     <row r="53" spans="1:8" ht="24.95" customHeight="1">
-      <c r="A53" s="105" t="s">
+      <c r="A53" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="B53" s="106"/>
-      <c r="C53" s="107"/>
+      <c r="B53" s="89"/>
+      <c r="C53" s="90"/>
       <c r="D53" s="84"/>
       <c r="E53" s="85"/>
       <c r="F53" s="84"/>
@@ -4060,6 +4060,19 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="G30:H37"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="B17:C18"/>
+    <mergeCell ref="F17:G17"/>
     <mergeCell ref="A53:C53"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A11:A12"/>
@@ -4076,19 +4089,6 @@
     <mergeCell ref="E38:F38"/>
     <mergeCell ref="G38:H38"/>
     <mergeCell ref="E30:F37"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="G30:H37"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="B17:C18"/>
-    <mergeCell ref="F17:G17"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.11811023622047245" bottom="0.11811023622047245" header="0.11811023622047245" footer="0.11811023622047245"/>
